--- a/dist-test/load-test-report.xlsx
+++ b/dist-test/load-test-report.xlsx
@@ -410,7 +410,7 @@
         <v>Generated on:</v>
       </c>
       <c r="B2" t="str">
-        <v>22/6/2026, 2:17:48 pm</v>
+        <v>22/6/2026, 2:30:09 pm</v>
       </c>
     </row>
     <row r="4">
@@ -813,13 +813,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F12" t="str">
-        <v>Fetch overhead took 10ms</v>
+        <v>Fetch overhead took 55ms</v>
       </c>
       <c r="G12" t="str">
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -839,13 +839,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F13" t="str">
-        <v>Fetch overhead took 42ms</v>
+        <v>Fetch overhead took 89ms</v>
       </c>
       <c r="G13" t="str">
         <v>PASS</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -865,13 +865,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F14" t="str">
-        <v>Fetch overhead took 21ms</v>
+        <v>Fetch overhead took 80ms</v>
       </c>
       <c r="G14" t="str">
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>21</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -891,13 +891,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F15" t="str">
-        <v>Fetch overhead took 47ms</v>
+        <v>Fetch overhead took 27ms</v>
       </c>
       <c r="G15" t="str">
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -917,13 +917,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F16" t="str">
-        <v>Fetch overhead took 32ms</v>
+        <v>Fetch overhead took 65ms</v>
       </c>
       <c r="G16" t="str">
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -943,13 +943,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F17" t="str">
-        <v>Fetch overhead took 17ms</v>
+        <v>Fetch overhead took 16ms</v>
       </c>
       <c r="G17" t="str">
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -969,13 +969,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F18" t="str">
-        <v>Fetch overhead took 27ms</v>
+        <v>Fetch overhead took 87ms</v>
       </c>
       <c r="G18" t="str">
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -995,13 +995,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F19" t="str">
-        <v>Fetch overhead took 30ms</v>
+        <v>Fetch overhead took 64ms</v>
       </c>
       <c r="G19" t="str">
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1021,13 +1021,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F20" t="str">
-        <v>Fetch overhead took 44ms</v>
+        <v>Fetch overhead took 37ms</v>
       </c>
       <c r="G20" t="str">
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -1047,13 +1047,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F21" t="str">
-        <v>Fetch overhead took 18ms</v>
+        <v>Fetch overhead took 15ms</v>
       </c>
       <c r="G21" t="str">
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1073,13 +1073,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F22" t="str">
-        <v>Fetch overhead took 71ms</v>
+        <v>Fetch overhead took 15ms</v>
       </c>
       <c r="G22" t="str">
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>71</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1099,13 +1099,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F23" t="str">
-        <v>Fetch overhead took 11ms</v>
+        <v>Fetch overhead took 37ms</v>
       </c>
       <c r="G23" t="str">
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -1125,13 +1125,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F24" t="str">
-        <v>Fetch overhead took 62ms</v>
+        <v>Fetch overhead took 74ms</v>
       </c>
       <c r="G24" t="str">
         <v>PASS</v>
       </c>
       <c r="H24">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
@@ -1151,13 +1151,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F25" t="str">
-        <v>Fetch overhead took 39ms</v>
+        <v>Fetch overhead took 66ms</v>
       </c>
       <c r="G25" t="str">
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -1177,13 +1177,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F26" t="str">
-        <v>Fetch overhead took 70ms</v>
+        <v>Fetch overhead took 75ms</v>
       </c>
       <c r="G26" t="str">
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -1203,13 +1203,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F27" t="str">
-        <v>Fetch overhead took 60ms</v>
+        <v>Fetch overhead took 29ms</v>
       </c>
       <c r="G27" t="str">
         <v>PASS</v>
       </c>
       <c r="H27">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
@@ -1229,13 +1229,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F28" t="str">
-        <v>Fetch overhead took 65ms</v>
+        <v>Fetch overhead took 83ms</v>
       </c>
       <c r="G28" t="str">
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -1255,13 +1255,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F29" t="str">
-        <v>Fetch overhead took 40ms</v>
+        <v>Fetch overhead took 57ms</v>
       </c>
       <c r="G29" t="str">
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
@@ -1281,13 +1281,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F30" t="str">
-        <v>Fetch overhead took 67ms</v>
+        <v>Fetch overhead took 77ms</v>
       </c>
       <c r="G30" t="str">
         <v>PASS</v>
       </c>
       <c r="H30">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
@@ -1307,13 +1307,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F31" t="str">
-        <v>Fetch overhead took 66ms</v>
+        <v>Fetch overhead took 70ms</v>
       </c>
       <c r="G31" t="str">
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
@@ -1333,13 +1333,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F32" t="str">
-        <v>Fetch overhead took 15ms</v>
+        <v>Fetch overhead took 26ms</v>
       </c>
       <c r="G32" t="str">
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
@@ -1359,13 +1359,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F33" t="str">
-        <v>Fetch overhead took 74ms</v>
+        <v>Fetch overhead took 21ms</v>
       </c>
       <c r="G33" t="str">
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1385,13 +1385,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F34" t="str">
-        <v>Fetch overhead took 51ms</v>
+        <v>Fetch overhead took 72ms</v>
       </c>
       <c r="G34" t="str">
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
@@ -1411,13 +1411,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F35" t="str">
-        <v>Fetch overhead took 57ms</v>
+        <v>Fetch overhead took 15ms</v>
       </c>
       <c r="G35" t="str">
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1437,13 +1437,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F36" t="str">
-        <v>Fetch overhead took 10ms</v>
+        <v>Fetch overhead took 61ms</v>
       </c>
       <c r="G36" t="str">
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>10</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -1463,13 +1463,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F37" t="str">
-        <v>Fetch overhead took 60ms</v>
+        <v>Fetch overhead took 68ms</v>
       </c>
       <c r="G37" t="str">
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -1489,13 +1489,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F38" t="str">
-        <v>Fetch overhead took 26ms</v>
+        <v>Fetch overhead took 85ms</v>
       </c>
       <c r="G38" t="str">
         <v>PASS</v>
       </c>
       <c r="H38">
-        <v>26</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
@@ -1515,13 +1515,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F39" t="str">
-        <v>Fetch overhead took 41ms</v>
+        <v>Fetch overhead took 26ms</v>
       </c>
       <c r="G39" t="str">
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
@@ -1541,13 +1541,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F40" t="str">
-        <v>Fetch overhead took 27ms</v>
+        <v>Fetch overhead took 44ms</v>
       </c>
       <c r="G40" t="str">
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -1567,13 +1567,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F41" t="str">
-        <v>Fetch overhead took 46ms</v>
+        <v>Fetch overhead took 76ms</v>
       </c>
       <c r="G41" t="str">
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>46</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
@@ -1593,13 +1593,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F42" t="str">
-        <v>Fetch overhead took 45ms</v>
+        <v>Fetch overhead took 10ms</v>
       </c>
       <c r="G42" t="str">
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1619,13 +1619,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F43" t="str">
-        <v>Fetch overhead took 85ms</v>
+        <v>Fetch overhead took 25ms</v>
       </c>
       <c r="G43" t="str">
         <v>PASS</v>
       </c>
       <c r="H43">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
@@ -1645,13 +1645,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F44" t="str">
-        <v>Fetch overhead took 35ms</v>
+        <v>Fetch overhead took 28ms</v>
       </c>
       <c r="G44" t="str">
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
@@ -1671,13 +1671,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F45" t="str">
-        <v>Fetch overhead took 50ms</v>
+        <v>Fetch overhead took 38ms</v>
       </c>
       <c r="G45" t="str">
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -1697,13 +1697,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F46" t="str">
-        <v>Fetch overhead took 47ms</v>
+        <v>Fetch overhead took 12ms</v>
       </c>
       <c r="G46" t="str">
         <v>PASS</v>
       </c>
       <c r="H46">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
@@ -1723,13 +1723,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F47" t="str">
-        <v>Fetch overhead took 43ms</v>
+        <v>Fetch overhead took 28ms</v>
       </c>
       <c r="G47" t="str">
         <v>PASS</v>
       </c>
       <c r="H47">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -1749,13 +1749,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F48" t="str">
-        <v>Fetch overhead took 86ms</v>
+        <v>Fetch overhead took 65ms</v>
       </c>
       <c r="G48" t="str">
         <v>PASS</v>
       </c>
       <c r="H48">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
@@ -1775,13 +1775,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F49" t="str">
-        <v>Fetch overhead took 54ms</v>
+        <v>Fetch overhead took 33ms</v>
       </c>
       <c r="G49" t="str">
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
@@ -1801,13 +1801,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F50" t="str">
-        <v>Fetch overhead took 32ms</v>
+        <v>Fetch overhead took 56ms</v>
       </c>
       <c r="G50" t="str">
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51">
@@ -1827,13 +1827,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F51" t="str">
-        <v>Fetch overhead took 30ms</v>
+        <v>Fetch overhead took 86ms</v>
       </c>
       <c r="G51" t="str">
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52">
@@ -1853,13 +1853,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F52" t="str">
-        <v>Fetch overhead took 62ms</v>
+        <v>Fetch overhead took 37ms</v>
       </c>
       <c r="G52" t="str">
         <v>PASS</v>
       </c>
       <c r="H52">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
@@ -1879,13 +1879,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F53" t="str">
-        <v>Fetch overhead took 28ms</v>
+        <v>Fetch overhead took 34ms</v>
       </c>
       <c r="G53" t="str">
         <v>PASS</v>
       </c>
       <c r="H53">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
@@ -1905,13 +1905,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F54" t="str">
-        <v>Fetch overhead took 87ms</v>
+        <v>Fetch overhead took 15ms</v>
       </c>
       <c r="G54" t="str">
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>87</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -1931,13 +1931,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F55" t="str">
-        <v>Fetch overhead took 15ms</v>
+        <v>Fetch overhead took 27ms</v>
       </c>
       <c r="G55" t="str">
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -1957,13 +1957,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F56" t="str">
-        <v>Fetch overhead took 63ms</v>
+        <v>Fetch overhead took 61ms</v>
       </c>
       <c r="G56" t="str">
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -1983,13 +1983,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F57" t="str">
-        <v>Fetch overhead took 68ms</v>
+        <v>Fetch overhead took 85ms</v>
       </c>
       <c r="G57" t="str">
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58">
@@ -2009,13 +2009,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F58" t="str">
-        <v>Fetch overhead took 20ms</v>
+        <v>Fetch overhead took 70ms</v>
       </c>
       <c r="G58" t="str">
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59">
@@ -2035,13 +2035,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F59" t="str">
-        <v>Fetch overhead took 69ms</v>
+        <v>Fetch overhead took 57ms</v>
       </c>
       <c r="G59" t="str">
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -2061,13 +2061,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F60" t="str">
-        <v>Fetch overhead took 34ms</v>
+        <v>Fetch overhead took 69ms</v>
       </c>
       <c r="G60" t="str">
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
@@ -2087,13 +2087,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F61" t="str">
-        <v>Fetch overhead took 77ms</v>
+        <v>Fetch overhead took 58ms</v>
       </c>
       <c r="G61" t="str">
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62">
@@ -2113,13 +2113,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F62" t="str">
-        <v>Fetch overhead took 78ms</v>
+        <v>Fetch overhead took 69ms</v>
       </c>
       <c r="G62" t="str">
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63">
@@ -2139,13 +2139,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F63" t="str">
-        <v>Fetch overhead took 86ms</v>
+        <v>Fetch overhead took 75ms</v>
       </c>
       <c r="G63" t="str">
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -2165,13 +2165,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F64" t="str">
-        <v>Fetch overhead took 27ms</v>
+        <v>Fetch overhead took 26ms</v>
       </c>
       <c r="G64" t="str">
         <v>PASS</v>
       </c>
       <c r="H64">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -2191,13 +2191,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F65" t="str">
-        <v>Fetch overhead took 19ms</v>
+        <v>Fetch overhead took 60ms</v>
       </c>
       <c r="G65" t="str">
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
@@ -2217,13 +2217,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F66" t="str">
-        <v>Fetch overhead took 55ms</v>
+        <v>Fetch overhead took 16ms</v>
       </c>
       <c r="G66" t="str">
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
@@ -2243,13 +2243,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F67" t="str">
-        <v>Fetch overhead took 69ms</v>
+        <v>Fetch overhead took 54ms</v>
       </c>
       <c r="G67" t="str">
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
@@ -2269,13 +2269,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F68" t="str">
-        <v>Fetch overhead took 10ms</v>
+        <v>Fetch overhead took 74ms</v>
       </c>
       <c r="G68" t="str">
         <v>PASS</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69">
@@ -2295,13 +2295,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F69" t="str">
-        <v>Fetch overhead took 67ms</v>
+        <v>Fetch overhead took 15ms</v>
       </c>
       <c r="G69" t="str">
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -2321,13 +2321,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F70" t="str">
-        <v>Fetch overhead took 16ms</v>
+        <v>Fetch overhead took 85ms</v>
       </c>
       <c r="G70" t="str">
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>16</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71">
@@ -2347,13 +2347,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F71" t="str">
-        <v>Fetch overhead took 79ms</v>
+        <v>Fetch overhead took 83ms</v>
       </c>
       <c r="G71" t="str">
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72">
@@ -2373,13 +2373,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F72" t="str">
-        <v>Fetch overhead took 30ms</v>
+        <v>Fetch overhead took 87ms</v>
       </c>
       <c r="G72" t="str">
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73">
@@ -2399,13 +2399,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F73" t="str">
-        <v>Fetch overhead took 32ms</v>
+        <v>Fetch overhead took 58ms</v>
       </c>
       <c r="G73" t="str">
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74">
@@ -2425,13 +2425,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F74" t="str">
-        <v>Fetch overhead took 28ms</v>
+        <v>Fetch overhead took 55ms</v>
       </c>
       <c r="G74" t="str">
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -2451,13 +2451,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F75" t="str">
-        <v>Fetch overhead took 44ms</v>
+        <v>Fetch overhead took 70ms</v>
       </c>
       <c r="G75" t="str">
         <v>PASS</v>
       </c>
       <c r="H75">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76">
@@ -2477,13 +2477,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F76" t="str">
-        <v>Fetch overhead took 27ms</v>
+        <v>Fetch overhead took 87ms</v>
       </c>
       <c r="G76" t="str">
         <v>PASS</v>
       </c>
       <c r="H76">
-        <v>27</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77">
@@ -2503,13 +2503,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F77" t="str">
-        <v>Fetch overhead took 26ms</v>
+        <v>Fetch overhead took 67ms</v>
       </c>
       <c r="G77" t="str">
         <v>PASS</v>
       </c>
       <c r="H77">
-        <v>26</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78">
@@ -2529,13 +2529,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F78" t="str">
-        <v>Fetch overhead took 31ms</v>
+        <v>Fetch overhead took 84ms</v>
       </c>
       <c r="G78" t="str">
         <v>PASS</v>
       </c>
       <c r="H78">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79">
@@ -2555,13 +2555,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F79" t="str">
-        <v>Fetch overhead took 82ms</v>
+        <v>Fetch overhead took 53ms</v>
       </c>
       <c r="G79" t="str">
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -2607,13 +2607,13 @@
         <v>Fetch load overhead &lt; 100ms</v>
       </c>
       <c r="F81" t="str">
-        <v>Fetch overhead took 81ms</v>
+        <v>Fetch overhead took 46ms</v>
       </c>
       <c r="G81" t="str">
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>81</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
@@ -2639,7 +2639,7 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -2665,7 +2665,7 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -2691,7 +2691,7 @@
         <v>PASS</v>
       </c>
       <c r="H84">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -2717,7 +2717,7 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86">
@@ -2743,7 +2743,7 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -2769,7 +2769,7 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -2795,7 +2795,7 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -2847,7 +2847,7 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
@@ -2873,7 +2873,7 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -2899,7 +2899,7 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
@@ -2925,7 +2925,7 @@
         <v>PASS</v>
       </c>
       <c r="H93">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
@@ -2951,7 +2951,7 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95">
@@ -2977,7 +2977,7 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -3003,7 +3003,7 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -3029,7 +3029,7 @@
         <v>PASS</v>
       </c>
       <c r="H97">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98">
@@ -3055,7 +3055,7 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99">
@@ -3081,7 +3081,7 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -3107,7 +3107,7 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101">
@@ -3133,7 +3133,7 @@
         <v>PASS</v>
       </c>
       <c r="H101">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102">
@@ -3159,7 +3159,7 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -3185,7 +3185,7 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104">
@@ -3211,7 +3211,7 @@
         <v>PASS</v>
       </c>
       <c r="H104">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -3237,7 +3237,7 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106">
@@ -3263,7 +3263,7 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
@@ -3289,7 +3289,7 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -3315,7 +3315,7 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109">
@@ -3341,7 +3341,7 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -3367,7 +3367,7 @@
         <v>PASS</v>
       </c>
       <c r="H110">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
@@ -3393,7 +3393,7 @@
         <v>PASS</v>
       </c>
       <c r="H111">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112">
@@ -3419,7 +3419,7 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
@@ -3445,7 +3445,7 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
@@ -3471,7 +3471,7 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="115">
@@ -3497,7 +3497,7 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
@@ -3523,7 +3523,7 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117">
@@ -3549,7 +3549,7 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118">
@@ -3575,7 +3575,7 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119">
@@ -3601,7 +3601,7 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120">
@@ -3627,7 +3627,7 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
@@ -3653,7 +3653,7 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
@@ -3679,7 +3679,7 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123">
@@ -3705,7 +3705,7 @@
         <v>PASS</v>
       </c>
       <c r="H123">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124">
@@ -3731,7 +3731,7 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125">
@@ -3757,7 +3757,7 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
@@ -3783,7 +3783,7 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127">
@@ -3809,7 +3809,7 @@
         <v>PASS</v>
       </c>
       <c r="H127">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
@@ -3835,7 +3835,7 @@
         <v>PASS</v>
       </c>
       <c r="H128">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129">
@@ -3861,7 +3861,7 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
@@ -3887,7 +3887,7 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="131">
@@ -3913,7 +3913,7 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132">
@@ -3939,7 +3939,7 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133">
@@ -3965,7 +3965,7 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134">
@@ -3991,7 +3991,7 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135">
@@ -4017,7 +4017,7 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="136">
@@ -4069,7 +4069,7 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138">
@@ -4095,7 +4095,7 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
@@ -4121,7 +4121,7 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140">
@@ -4147,7 +4147,7 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141">
@@ -4173,7 +4173,7 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -4199,7 +4199,7 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -4225,7 +4225,7 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
@@ -4251,7 +4251,7 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
@@ -4277,7 +4277,7 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -4303,7 +4303,7 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147">
@@ -4329,7 +4329,7 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148">
@@ -4355,7 +4355,7 @@
         <v>PASS</v>
       </c>
       <c r="H148">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
@@ -4381,7 +4381,7 @@
         <v>PASS</v>
       </c>
       <c r="H149">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -4407,7 +4407,7 @@
         <v>PASS</v>
       </c>
       <c r="H150">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151">
@@ -4433,7 +4433,7 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152">
@@ -4459,7 +4459,7 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153">
@@ -4485,7 +4485,7 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="154">
@@ -4511,7 +4511,7 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155">
@@ -4537,7 +4537,7 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156">
@@ -4563,7 +4563,7 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157">
@@ -4589,7 +4589,7 @@
         <v>PASS</v>
       </c>
       <c r="H157">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158">
@@ -4615,7 +4615,7 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159">
@@ -4641,7 +4641,7 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="160">
@@ -4667,7 +4667,7 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161">
@@ -4693,7 +4693,7 @@
         <v>PASS</v>
       </c>
       <c r="H161">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -4719,7 +4719,7 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="163">
@@ -4745,7 +4745,7 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164">
@@ -4771,7 +4771,7 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165">
@@ -4797,7 +4797,7 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166">
@@ -4823,7 +4823,7 @@
         <v>PASS</v>
       </c>
       <c r="H166">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
@@ -4849,7 +4849,7 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
@@ -4875,7 +4875,7 @@
         <v>PASS</v>
       </c>
       <c r="H168">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169">
@@ -4901,7 +4901,7 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170">
@@ -4927,7 +4927,7 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -4953,7 +4953,7 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172">
@@ -4979,7 +4979,7 @@
         <v>PASS</v>
       </c>
       <c r="H172">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173">
@@ -5005,7 +5005,7 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174">
@@ -5031,7 +5031,7 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175">
@@ -5057,7 +5057,7 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="176">
@@ -5083,7 +5083,7 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
@@ -5109,7 +5109,7 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178">
@@ -5135,7 +5135,7 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
@@ -5161,7 +5161,7 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180">
@@ -5187,7 +5187,7 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181">
@@ -5213,7 +5213,7 @@
         <v>PASS</v>
       </c>
       <c r="H181">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182">
@@ -5239,7 +5239,7 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183">
@@ -5265,7 +5265,7 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="184">
@@ -5291,7 +5291,7 @@
         <v>PASS</v>
       </c>
       <c r="H184">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185">
@@ -5317,7 +5317,7 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -5343,7 +5343,7 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187">
@@ -5369,7 +5369,7 @@
         <v>PASS</v>
       </c>
       <c r="H187">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188">
@@ -5395,7 +5395,7 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189">
@@ -5421,7 +5421,7 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190">
@@ -5447,7 +5447,7 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191">
@@ -5473,7 +5473,7 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
@@ -5499,7 +5499,7 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
@@ -5525,7 +5525,7 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194">
@@ -5551,7 +5551,7 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195">
@@ -5577,7 +5577,7 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="196">
@@ -5603,7 +5603,7 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197">
@@ -5629,7 +5629,7 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -5681,7 +5681,7 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200">
@@ -5707,7 +5707,7 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201">
@@ -5733,7 +5733,7 @@
         <v>PASS</v>
       </c>
       <c r="H201">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202">
@@ -5759,7 +5759,7 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5785,7 +5785,7 @@
         <v>PASS</v>
       </c>
       <c r="H203">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204">
@@ -5811,7 +5811,7 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205">
@@ -5837,7 +5837,7 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206">
@@ -5863,7 +5863,7 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207">
@@ -5889,7 +5889,7 @@
         <v>PASS</v>
       </c>
       <c r="H207">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="208">
@@ -5915,7 +5915,7 @@
         <v>PASS</v>
       </c>
       <c r="H208">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209">
@@ -5941,7 +5941,7 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -5967,7 +5967,7 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211">
@@ -5993,7 +5993,7 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212">
@@ -6019,7 +6019,7 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="213">
@@ -6045,7 +6045,7 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
@@ -6071,7 +6071,7 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215">
@@ -6097,7 +6097,7 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216">
@@ -6123,7 +6123,7 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217">
@@ -6149,7 +6149,7 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218">
@@ -6175,7 +6175,7 @@
         <v>PASS</v>
       </c>
       <c r="H218">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219">
@@ -6201,7 +6201,7 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -6227,7 +6227,7 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
@@ -6253,7 +6253,7 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="222">
@@ -6279,7 +6279,7 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="223">
@@ -6305,7 +6305,7 @@
         <v>PASS</v>
       </c>
       <c r="H223">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224">
@@ -6331,7 +6331,7 @@
         <v>PASS</v>
       </c>
       <c r="H224">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225">
@@ -6357,7 +6357,7 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226">
@@ -6383,7 +6383,7 @@
         <v>PASS</v>
       </c>
       <c r="H226">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227">
@@ -6409,7 +6409,7 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228">
@@ -6435,7 +6435,7 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229">
@@ -6461,7 +6461,7 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230">
@@ -6487,7 +6487,7 @@
         <v>PASS</v>
       </c>
       <c r="H230">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
@@ -6513,7 +6513,7 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232">
@@ -6539,7 +6539,7 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="233">
@@ -6591,7 +6591,7 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
@@ -6617,7 +6617,7 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236">
@@ -6643,7 +6643,7 @@
         <v>PASS</v>
       </c>
       <c r="H236">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237">
@@ -6669,7 +6669,7 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="238">
@@ -6695,7 +6695,7 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
@@ -6721,7 +6721,7 @@
         <v>PASS</v>
       </c>
       <c r="H239">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="240">
@@ -6747,7 +6747,7 @@
         <v>PASS</v>
       </c>
       <c r="H240">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241">
@@ -6773,7 +6773,7 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="242">
@@ -6799,7 +6799,7 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
@@ -6825,7 +6825,7 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244">
@@ -6851,7 +6851,7 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245">
@@ -6877,7 +6877,7 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -6903,7 +6903,7 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -6929,7 +6929,7 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -6955,7 +6955,7 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -6981,7 +6981,7 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250">
@@ -7007,7 +7007,7 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="251">
@@ -7033,7 +7033,7 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
@@ -7059,7 +7059,7 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253">
@@ -7085,7 +7085,7 @@
         <v>PASS</v>
       </c>
       <c r="H253">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
@@ -7111,7 +7111,7 @@
         <v>PASS</v>
       </c>
       <c r="H254">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7137,7 +7137,7 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256">
@@ -7163,7 +7163,7 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257">
@@ -7189,7 +7189,7 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258">
@@ -7215,7 +7215,7 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259">
@@ -7241,7 +7241,7 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="260">
@@ -7267,7 +7267,7 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -7293,7 +7293,7 @@
         <v>PASS</v>
       </c>
       <c r="H261">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="262">
@@ -7319,7 +7319,7 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="263">
@@ -7345,7 +7345,7 @@
         <v>PASS</v>
       </c>
       <c r="H263">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -7371,7 +7371,7 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265">
@@ -7397,7 +7397,7 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266">
@@ -7423,7 +7423,7 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="267">
@@ -7449,7 +7449,7 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -7475,7 +7475,7 @@
         <v>PASS</v>
       </c>
       <c r="H268">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="269">
@@ -7501,7 +7501,7 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="270">
@@ -7527,7 +7527,7 @@
         <v>PASS</v>
       </c>
       <c r="H270">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7553,7 +7553,7 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272">
@@ -7579,7 +7579,7 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -7605,7 +7605,7 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="274">
@@ -7631,7 +7631,7 @@
         <v>PASS</v>
       </c>
       <c r="H274">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="275">
@@ -7657,7 +7657,7 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="276">
@@ -7683,7 +7683,7 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277">
@@ -7709,7 +7709,7 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278">
@@ -7735,7 +7735,7 @@
         <v>PASS</v>
       </c>
       <c r="H278">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -7761,7 +7761,7 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="280">
@@ -7787,7 +7787,7 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281">
@@ -7813,7 +7813,7 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282">
@@ -7839,7 +7839,7 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
@@ -7865,7 +7865,7 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="284">
@@ -7891,7 +7891,7 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
@@ -7917,7 +7917,7 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -7943,7 +7943,7 @@
         <v>PASS</v>
       </c>
       <c r="H286">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="287">
@@ -7969,7 +7969,7 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
@@ -8021,7 +8021,7 @@
         <v>PASS</v>
       </c>
       <c r="H289">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290">
@@ -8047,7 +8047,7 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8073,7 +8073,7 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
@@ -8099,7 +8099,7 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293">
@@ -8125,7 +8125,7 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="294">
@@ -8151,7 +8151,7 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -8177,7 +8177,7 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296">
@@ -8203,7 +8203,7 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -8229,7 +8229,7 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298">
@@ -8255,7 +8255,7 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299">
@@ -8281,7 +8281,7 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300">
@@ -8307,7 +8307,7 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301">
@@ -8333,7 +8333,7 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="302">
@@ -8353,13 +8353,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F302" t="str">
-        <v>Measured latency is 56ms</v>
+        <v>Measured latency is 42ms</v>
       </c>
       <c r="G302" t="str">
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="303">
@@ -8379,13 +8379,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F303" t="str">
-        <v>Measured latency is 54ms</v>
+        <v>Measured latency is 30ms</v>
       </c>
       <c r="G303" t="str">
         <v>PASS</v>
       </c>
       <c r="H303">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="304">
@@ -8405,13 +8405,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F304" t="str">
-        <v>Measured latency is 17ms</v>
+        <v>Measured latency is 16ms</v>
       </c>
       <c r="G304" t="str">
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="305">
@@ -8431,13 +8431,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F305" t="str">
-        <v>Measured latency is 18ms</v>
+        <v>Measured latency is 88ms</v>
       </c>
       <c r="G305" t="str">
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>18</v>
+        <v>88</v>
       </c>
     </row>
     <row r="306">
@@ -8457,13 +8457,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F306" t="str">
-        <v>Measured latency is 79ms</v>
+        <v>Measured latency is 71ms</v>
       </c>
       <c r="G306" t="str">
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="307">
@@ -8483,13 +8483,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F307" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 33ms</v>
       </c>
       <c r="G307" t="str">
         <v>PASS</v>
       </c>
       <c r="H307">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="308">
@@ -8509,13 +8509,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F308" t="str">
-        <v>Measured latency is 35ms</v>
+        <v>Measured latency is 83ms</v>
       </c>
       <c r="G308" t="str">
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="309">
@@ -8535,13 +8535,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F309" t="str">
-        <v>Measured latency is 39ms</v>
+        <v>Measured latency is 70ms</v>
       </c>
       <c r="G309" t="str">
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="310">
@@ -8561,13 +8561,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F310" t="str">
-        <v>Measured latency is 32ms</v>
+        <v>Measured latency is 56ms</v>
       </c>
       <c r="G310" t="str">
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="311">
@@ -8587,13 +8587,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F311" t="str">
-        <v>Measured latency is 17ms</v>
+        <v>Measured latency is 10ms</v>
       </c>
       <c r="G311" t="str">
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312">
@@ -8613,13 +8613,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F312" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 59ms</v>
       </c>
       <c r="G312" t="str">
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="313">
@@ -8639,13 +8639,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F313" t="str">
-        <v>Measured latency is 43ms</v>
+        <v>Measured latency is 24ms</v>
       </c>
       <c r="G313" t="str">
         <v>PASS</v>
       </c>
       <c r="H313">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="314">
@@ -8665,13 +8665,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F314" t="str">
-        <v>Measured latency is 24ms</v>
+        <v>Measured latency is 35ms</v>
       </c>
       <c r="G314" t="str">
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="315">
@@ -8691,13 +8691,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F315" t="str">
-        <v>Measured latency is 71ms</v>
+        <v>Measured latency is 46ms</v>
       </c>
       <c r="G315" t="str">
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>71</v>
+        <v>46</v>
       </c>
     </row>
     <row r="316">
@@ -8717,13 +8717,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F316" t="str">
-        <v>Measured latency is 13ms</v>
+        <v>Measured latency is 43ms</v>
       </c>
       <c r="G316" t="str">
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="317">
@@ -8743,13 +8743,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F317" t="str">
-        <v>Measured latency is 75ms</v>
+        <v>Measured latency is 38ms</v>
       </c>
       <c r="G317" t="str">
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="318">
@@ -8769,13 +8769,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F318" t="str">
-        <v>Measured latency is 42ms</v>
+        <v>Measured latency is 48ms</v>
       </c>
       <c r="G318" t="str">
         <v>PASS</v>
       </c>
       <c r="H318">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="319">
@@ -8795,13 +8795,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F319" t="str">
-        <v>Measured latency is 46ms</v>
+        <v>Measured latency is 64ms</v>
       </c>
       <c r="G319" t="str">
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="320">
@@ -8821,13 +8821,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F320" t="str">
-        <v>Measured latency is 38ms</v>
+        <v>Measured latency is 22ms</v>
       </c>
       <c r="G320" t="str">
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321">
@@ -8847,13 +8847,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F321" t="str">
-        <v>Measured latency is 88ms</v>
+        <v>Measured latency is 49ms</v>
       </c>
       <c r="G321" t="str">
         <v>PASS</v>
       </c>
       <c r="H321">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="322">
@@ -8873,13 +8873,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F322" t="str">
-        <v>Measured latency is 72ms</v>
+        <v>Measured latency is 27ms</v>
       </c>
       <c r="G322" t="str">
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="323">
@@ -8899,13 +8899,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F323" t="str">
-        <v>Measured latency is 26ms</v>
+        <v>Measured latency is 34ms</v>
       </c>
       <c r="G323" t="str">
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="324">
@@ -8925,13 +8925,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F324" t="str">
-        <v>Measured latency is 42ms</v>
+        <v>Measured latency is 57ms</v>
       </c>
       <c r="G324" t="str">
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="325">
@@ -8951,13 +8951,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F325" t="str">
-        <v>Measured latency is 19ms</v>
+        <v>Measured latency is 28ms</v>
       </c>
       <c r="G325" t="str">
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="326">
@@ -8977,13 +8977,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F326" t="str">
-        <v>Measured latency is 37ms</v>
+        <v>Measured latency is 13ms</v>
       </c>
       <c r="G326" t="str">
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="327">
@@ -9003,13 +9003,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F327" t="str">
-        <v>Measured latency is 82ms</v>
+        <v>Measured latency is 49ms</v>
       </c>
       <c r="G327" t="str">
         <v>PASS</v>
       </c>
       <c r="H327">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="328">
@@ -9029,13 +9029,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F328" t="str">
-        <v>Measured latency is 73ms</v>
+        <v>Measured latency is 82ms</v>
       </c>
       <c r="G328" t="str">
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="329">
@@ -9055,13 +9055,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F329" t="str">
-        <v>Measured latency is 24ms</v>
+        <v>Measured latency is 27ms</v>
       </c>
       <c r="G329" t="str">
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330">
@@ -9081,13 +9081,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F330" t="str">
-        <v>Measured latency is 55ms</v>
+        <v>Measured latency is 46ms</v>
       </c>
       <c r="G330" t="str">
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="331">
@@ -9107,13 +9107,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F331" t="str">
-        <v>Measured latency is 63ms</v>
+        <v>Measured latency is 61ms</v>
       </c>
       <c r="G331" t="str">
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="332">
@@ -9133,13 +9133,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F332" t="str">
-        <v>Measured latency is 37ms</v>
+        <v>Measured latency is 69ms</v>
       </c>
       <c r="G332" t="str">
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="333">
@@ -9159,13 +9159,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F333" t="str">
-        <v>Measured latency is 31ms</v>
+        <v>Measured latency is 70ms</v>
       </c>
       <c r="G333" t="str">
         <v>PASS</v>
       </c>
       <c r="H333">
-        <v>31</v>
+        <v>70</v>
       </c>
     </row>
     <row r="334">
@@ -9185,13 +9185,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F334" t="str">
-        <v>Measured latency is 53ms</v>
+        <v>Measured latency is 41ms</v>
       </c>
       <c r="G334" t="str">
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="335">
@@ -9211,13 +9211,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F335" t="str">
-        <v>Measured latency is 84ms</v>
+        <v>Measured latency is 29ms</v>
       </c>
       <c r="G335" t="str">
         <v>PASS</v>
       </c>
       <c r="H335">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="336">
@@ -9237,13 +9237,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F336" t="str">
-        <v>Measured latency is 47ms</v>
+        <v>Measured latency is 23ms</v>
       </c>
       <c r="G336" t="str">
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="337">
@@ -9263,13 +9263,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F337" t="str">
-        <v>Measured latency is 14ms</v>
+        <v>Measured latency is 22ms</v>
       </c>
       <c r="G337" t="str">
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="338">
@@ -9289,13 +9289,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F338" t="str">
-        <v>Measured latency is 84ms</v>
+        <v>Measured latency is 41ms</v>
       </c>
       <c r="G338" t="str">
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="339">
@@ -9315,13 +9315,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F339" t="str">
-        <v>Measured latency is 17ms</v>
+        <v>Measured latency is 26ms</v>
       </c>
       <c r="G339" t="str">
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="340">
@@ -9341,13 +9341,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F340" t="str">
-        <v>Measured latency is 89ms</v>
+        <v>Measured latency is 70ms</v>
       </c>
       <c r="G340" t="str">
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="341">
@@ -9367,13 +9367,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F341" t="str">
-        <v>Measured latency is 42ms</v>
+        <v>Measured latency is 60ms</v>
       </c>
       <c r="G341" t="str">
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="342">
@@ -9393,13 +9393,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F342" t="str">
-        <v>Measured latency is 56ms</v>
+        <v>Measured latency is 45ms</v>
       </c>
       <c r="G342" t="str">
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="343">
@@ -9419,13 +9419,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F343" t="str">
-        <v>Measured latency is 33ms</v>
+        <v>Measured latency is 83ms</v>
       </c>
       <c r="G343" t="str">
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="344">
@@ -9445,13 +9445,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F344" t="str">
-        <v>Measured latency is 87ms</v>
+        <v>Measured latency is 69ms</v>
       </c>
       <c r="G344" t="str">
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="345">
@@ -9471,13 +9471,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F345" t="str">
-        <v>Measured latency is 53ms</v>
+        <v>Measured latency is 13ms</v>
       </c>
       <c r="G345" t="str">
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="346">
@@ -9497,13 +9497,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F346" t="str">
-        <v>Measured latency is 30ms</v>
+        <v>Measured latency is 79ms</v>
       </c>
       <c r="G346" t="str">
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="347">
@@ -9523,13 +9523,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F347" t="str">
-        <v>Measured latency is 24ms</v>
+        <v>Measured latency is 41ms</v>
       </c>
       <c r="G347" t="str">
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="348">
@@ -9549,13 +9549,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F348" t="str">
-        <v>Measured latency is 82ms</v>
+        <v>Measured latency is 18ms</v>
       </c>
       <c r="G348" t="str">
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>82</v>
+        <v>18</v>
       </c>
     </row>
     <row r="349">
@@ -9575,13 +9575,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F349" t="str">
-        <v>Measured latency is 18ms</v>
+        <v>Measured latency is 40ms</v>
       </c>
       <c r="G349" t="str">
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="350">
@@ -9601,13 +9601,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F350" t="str">
-        <v>Measured latency is 80ms</v>
+        <v>Measured latency is 11ms</v>
       </c>
       <c r="G350" t="str">
         <v>PASS</v>
       </c>
       <c r="H350">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="351">
@@ -9627,13 +9627,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F351" t="str">
-        <v>Measured latency is 56ms</v>
+        <v>Measured latency is 78ms</v>
       </c>
       <c r="G351" t="str">
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="352">
@@ -9653,13 +9653,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F352" t="str">
-        <v>Measured latency is 58ms</v>
+        <v>Measured latency is 32ms</v>
       </c>
       <c r="G352" t="str">
         <v>PASS</v>
       </c>
       <c r="H352">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="353">
@@ -9679,13 +9679,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F353" t="str">
-        <v>Measured latency is 35ms</v>
+        <v>Measured latency is 73ms</v>
       </c>
       <c r="G353" t="str">
         <v>PASS</v>
       </c>
       <c r="H353">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="354">
@@ -9705,13 +9705,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F354" t="str">
-        <v>Measured latency is 18ms</v>
+        <v>Measured latency is 67ms</v>
       </c>
       <c r="G354" t="str">
         <v>PASS</v>
       </c>
       <c r="H354">
-        <v>18</v>
+        <v>67</v>
       </c>
     </row>
     <row r="355">
@@ -9731,13 +9731,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F355" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 89ms</v>
       </c>
       <c r="G355" t="str">
         <v>PASS</v>
       </c>
       <c r="H355">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="356">
@@ -9757,13 +9757,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F356" t="str">
-        <v>Measured latency is 36ms</v>
+        <v>Measured latency is 75ms</v>
       </c>
       <c r="G356" t="str">
         <v>PASS</v>
       </c>
       <c r="H356">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="357">
@@ -9783,13 +9783,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F357" t="str">
-        <v>Measured latency is 12ms</v>
+        <v>Measured latency is 66ms</v>
       </c>
       <c r="G357" t="str">
         <v>PASS</v>
       </c>
       <c r="H357">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="358">
@@ -9809,13 +9809,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F358" t="str">
-        <v>Measured latency is 63ms</v>
+        <v>Measured latency is 40ms</v>
       </c>
       <c r="G358" t="str">
         <v>PASS</v>
       </c>
       <c r="H358">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="359">
@@ -9835,13 +9835,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F359" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 23ms</v>
       </c>
       <c r="G359" t="str">
         <v>PASS</v>
       </c>
       <c r="H359">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360">
@@ -9861,13 +9861,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F360" t="str">
-        <v>Measured latency is 49ms</v>
+        <v>Measured latency is 39ms</v>
       </c>
       <c r="G360" t="str">
         <v>PASS</v>
       </c>
       <c r="H360">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="361">
@@ -9887,13 +9887,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F361" t="str">
-        <v>Measured latency is 58ms</v>
+        <v>Measured latency is 81ms</v>
       </c>
       <c r="G361" t="str">
         <v>PASS</v>
       </c>
       <c r="H361">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="362">
@@ -9913,13 +9913,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F362" t="str">
-        <v>Measured latency is 59ms</v>
+        <v>Measured latency is 85ms</v>
       </c>
       <c r="G362" t="str">
         <v>PASS</v>
       </c>
       <c r="H362">
-        <v>59</v>
+        <v>85</v>
       </c>
     </row>
     <row r="363">
@@ -9939,13 +9939,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F363" t="str">
-        <v>Measured latency is 77ms</v>
+        <v>Measured latency is 37ms</v>
       </c>
       <c r="G363" t="str">
         <v>PASS</v>
       </c>
       <c r="H363">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="364">
@@ -9965,13 +9965,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F364" t="str">
-        <v>Measured latency is 83ms</v>
+        <v>Measured latency is 78ms</v>
       </c>
       <c r="G364" t="str">
         <v>PASS</v>
       </c>
       <c r="H364">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="365">
@@ -9991,13 +9991,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F365" t="str">
-        <v>Measured latency is 73ms</v>
+        <v>Measured latency is 77ms</v>
       </c>
       <c r="G365" t="str">
         <v>PASS</v>
       </c>
       <c r="H365">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="366">
@@ -10017,13 +10017,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F366" t="str">
-        <v>Measured latency is 13ms</v>
+        <v>Measured latency is 47ms</v>
       </c>
       <c r="G366" t="str">
         <v>PASS</v>
       </c>
       <c r="H366">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="367">
@@ -10043,13 +10043,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F367" t="str">
-        <v>Measured latency is 55ms</v>
+        <v>Measured latency is 78ms</v>
       </c>
       <c r="G367" t="str">
         <v>PASS</v>
       </c>
       <c r="H367">
-        <v>55</v>
+        <v>78</v>
       </c>
     </row>
     <row r="368">
@@ -10069,13 +10069,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F368" t="str">
-        <v>Measured latency is 76ms</v>
+        <v>Measured latency is 68ms</v>
       </c>
       <c r="G368" t="str">
         <v>PASS</v>
       </c>
       <c r="H368">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="369">
@@ -10095,13 +10095,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F369" t="str">
-        <v>Measured latency is 20ms</v>
+        <v>Measured latency is 49ms</v>
       </c>
       <c r="G369" t="str">
         <v>PASS</v>
       </c>
       <c r="H369">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="370">
@@ -10121,13 +10121,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F370" t="str">
-        <v>Measured latency is 70ms</v>
+        <v>Measured latency is 72ms</v>
       </c>
       <c r="G370" t="str">
         <v>PASS</v>
       </c>
       <c r="H370">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="371">
@@ -10147,13 +10147,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F371" t="str">
-        <v>Measured latency is 16ms</v>
+        <v>Measured latency is 80ms</v>
       </c>
       <c r="G371" t="str">
         <v>PASS</v>
       </c>
       <c r="H371">
-        <v>16</v>
+        <v>80</v>
       </c>
     </row>
     <row r="372">
@@ -10173,13 +10173,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F372" t="str">
-        <v>Measured latency is 73ms</v>
+        <v>Measured latency is 30ms</v>
       </c>
       <c r="G372" t="str">
         <v>PASS</v>
       </c>
       <c r="H372">
-        <v>73</v>
+        <v>30</v>
       </c>
     </row>
     <row r="373">
@@ -10199,13 +10199,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F373" t="str">
-        <v>Measured latency is 74ms</v>
+        <v>Measured latency is 44ms</v>
       </c>
       <c r="G373" t="str">
         <v>PASS</v>
       </c>
       <c r="H373">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="374">
@@ -10225,13 +10225,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F374" t="str">
-        <v>Measured latency is 80ms</v>
+        <v>Measured latency is 43ms</v>
       </c>
       <c r="G374" t="str">
         <v>PASS</v>
       </c>
       <c r="H374">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="375">
@@ -10251,13 +10251,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F375" t="str">
-        <v>Measured latency is 75ms</v>
+        <v>Measured latency is 32ms</v>
       </c>
       <c r="G375" t="str">
         <v>PASS</v>
       </c>
       <c r="H375">
-        <v>75</v>
+        <v>32</v>
       </c>
     </row>
     <row r="376">
@@ -10277,13 +10277,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F376" t="str">
-        <v>Measured latency is 16ms</v>
+        <v>Measured latency is 41ms</v>
       </c>
       <c r="G376" t="str">
         <v>PASS</v>
       </c>
       <c r="H376">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="377">
@@ -10303,13 +10303,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F377" t="str">
-        <v>Measured latency is 15ms</v>
+        <v>Measured latency is 68ms</v>
       </c>
       <c r="G377" t="str">
         <v>PASS</v>
       </c>
       <c r="H377">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="378">
@@ -10329,13 +10329,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F378" t="str">
-        <v>Measured latency is 44ms</v>
+        <v>Measured latency is 27ms</v>
       </c>
       <c r="G378" t="str">
         <v>PASS</v>
       </c>
       <c r="H378">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="379">
@@ -10355,13 +10355,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F379" t="str">
-        <v>Measured latency is 87ms</v>
+        <v>Measured latency is 50ms</v>
       </c>
       <c r="G379" t="str">
         <v>PASS</v>
       </c>
       <c r="H379">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="380">
@@ -10381,13 +10381,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F380" t="str">
-        <v>Measured latency is 18ms</v>
+        <v>Measured latency is 19ms</v>
       </c>
       <c r="G380" t="str">
         <v>PASS</v>
       </c>
       <c r="H380">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="381">
@@ -10407,13 +10407,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F381" t="str">
-        <v>Measured latency is 21ms</v>
+        <v>Measured latency is 58ms</v>
       </c>
       <c r="G381" t="str">
         <v>PASS</v>
       </c>
       <c r="H381">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="382">
@@ -10433,13 +10433,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F382" t="str">
-        <v>Measured latency is 84ms</v>
+        <v>Measured latency is 11ms</v>
       </c>
       <c r="G382" t="str">
         <v>PASS</v>
       </c>
       <c r="H382">
-        <v>84</v>
+        <v>11</v>
       </c>
     </row>
     <row r="383">
@@ -10459,13 +10459,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F383" t="str">
-        <v>Measured latency is 38ms</v>
+        <v>Measured latency is 77ms</v>
       </c>
       <c r="G383" t="str">
         <v>PASS</v>
       </c>
       <c r="H383">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="384">
@@ -10485,13 +10485,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F384" t="str">
-        <v>Measured latency is 31ms</v>
+        <v>Measured latency is 61ms</v>
       </c>
       <c r="G384" t="str">
         <v>PASS</v>
       </c>
       <c r="H384">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="385">
@@ -10511,13 +10511,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F385" t="str">
-        <v>Measured latency is 45ms</v>
+        <v>Measured latency is 69ms</v>
       </c>
       <c r="G385" t="str">
         <v>PASS</v>
       </c>
       <c r="H385">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="386">
@@ -10537,13 +10537,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F386" t="str">
-        <v>Measured latency is 77ms</v>
+        <v>Measured latency is 41ms</v>
       </c>
       <c r="G386" t="str">
         <v>PASS</v>
       </c>
       <c r="H386">
-        <v>77</v>
+        <v>41</v>
       </c>
     </row>
     <row r="387">
@@ -10563,13 +10563,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F387" t="str">
-        <v>Measured latency is 58ms</v>
+        <v>Measured latency is 40ms</v>
       </c>
       <c r="G387" t="str">
         <v>PASS</v>
       </c>
       <c r="H387">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388">
@@ -10589,13 +10589,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F388" t="str">
-        <v>Measured latency is 11ms</v>
+        <v>Measured latency is 39ms</v>
       </c>
       <c r="G388" t="str">
         <v>PASS</v>
       </c>
       <c r="H388">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="389">
@@ -10615,13 +10615,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F389" t="str">
-        <v>Measured latency is 75ms</v>
+        <v>Measured latency is 23ms</v>
       </c>
       <c r="G389" t="str">
         <v>PASS</v>
       </c>
       <c r="H389">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="390">
@@ -10641,13 +10641,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F390" t="str">
-        <v>Measured latency is 22ms</v>
+        <v>Measured latency is 70ms</v>
       </c>
       <c r="G390" t="str">
         <v>PASS</v>
       </c>
       <c r="H390">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="391">
@@ -10667,13 +10667,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F391" t="str">
-        <v>Measured latency is 75ms</v>
+        <v>Measured latency is 50ms</v>
       </c>
       <c r="G391" t="str">
         <v>PASS</v>
       </c>
       <c r="H391">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="392">
@@ -10693,13 +10693,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F392" t="str">
-        <v>Measured latency is 32ms</v>
+        <v>Measured latency is 50ms</v>
       </c>
       <c r="G392" t="str">
         <v>PASS</v>
       </c>
       <c r="H392">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="393">
@@ -10719,13 +10719,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F393" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 60ms</v>
       </c>
       <c r="G393" t="str">
         <v>PASS</v>
       </c>
       <c r="H393">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="394">
@@ -10745,13 +10745,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F394" t="str">
-        <v>Measured latency is 27ms</v>
+        <v>Measured latency is 43ms</v>
       </c>
       <c r="G394" t="str">
         <v>PASS</v>
       </c>
       <c r="H394">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="395">
@@ -10771,13 +10771,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F395" t="str">
-        <v>Measured latency is 36ms</v>
+        <v>Measured latency is 86ms</v>
       </c>
       <c r="G395" t="str">
         <v>PASS</v>
       </c>
       <c r="H395">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="396">
@@ -10797,13 +10797,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F396" t="str">
-        <v>Measured latency is 36ms</v>
+        <v>Measured latency is 84ms</v>
       </c>
       <c r="G396" t="str">
         <v>PASS</v>
       </c>
       <c r="H396">
-        <v>36</v>
+        <v>84</v>
       </c>
     </row>
     <row r="397">
@@ -10823,13 +10823,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F397" t="str">
-        <v>Measured latency is 48ms</v>
+        <v>Measured latency is 81ms</v>
       </c>
       <c r="G397" t="str">
         <v>PASS</v>
       </c>
       <c r="H397">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="398">
@@ -10849,13 +10849,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F398" t="str">
-        <v>Measured latency is 73ms</v>
+        <v>Measured latency is 70ms</v>
       </c>
       <c r="G398" t="str">
         <v>PASS</v>
       </c>
       <c r="H398">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="399">
@@ -10875,13 +10875,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F399" t="str">
-        <v>Measured latency is 45ms</v>
+        <v>Measured latency is 77ms</v>
       </c>
       <c r="G399" t="str">
         <v>PASS</v>
       </c>
       <c r="H399">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="400">
@@ -10901,13 +10901,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F400" t="str">
-        <v>Measured latency is 34ms</v>
+        <v>Measured latency is 51ms</v>
       </c>
       <c r="G400" t="str">
         <v>PASS</v>
       </c>
       <c r="H400">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="401">
@@ -10927,13 +10927,13 @@
         <v>Response latency &lt; 100ms</v>
       </c>
       <c r="F401" t="str">
-        <v>Measured latency is 77ms</v>
+        <v>Measured latency is 83ms</v>
       </c>
       <c r="G401" t="str">
         <v>PASS</v>
       </c>
       <c r="H401">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
